--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487644_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487644_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0844</v>
+        <v>1.9212</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8487</v>
+        <v>-0.4668</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9331</v>
+        <v>2.388</v>
       </c>
       <c r="G2" t="n">
         <v>2.1991</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6898</v>
+        <v>0.5266</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0954</v>
+        <v>0.2865</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7852</v>
+        <v>0.2401</v>
       </c>
       <c r="V2" t="n">
         <v>0.9418</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5631</v>
+        <v>1.208</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1291</v>
+        <v>0.5518</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5659999999999999</v>
+        <v>0.6562</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7972</v>
+        <v>0.0441</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7571</v>
+        <v>-0.4548</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0401</v>
+        <v>0.4988</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6353</v>
+        <v>1.3714</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3718</v>
+        <v>0.7168</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2635</v>
+        <v>0.6546</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8381</v>
+        <v>-1.3273</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6146</v>
+        <v>-1.1716</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2235</v>
+        <v>-0.1557</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1281</v>
+        <v>0.2297</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4599</v>
+        <v>-0.0076</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6682</v>
+        <v>0.2373</v>
       </c>
       <c r="V3" t="n">
-        <v>0.894</v>
+        <v>1.1283</v>
       </c>
       <c r="W3" t="n">
-        <v>0.894</v>
+        <v>1.1283</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4252</v>
+        <v>1.1481</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5308</v>
+        <v>1.5506</v>
       </c>
       <c r="F4" t="n">
-        <v>0.956</v>
+        <v>-0.4025</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0441</v>
+        <v>0.7972</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4548</v>
+        <v>0.7571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4988</v>
+        <v>0.0401</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3714</v>
+        <v>2.6353</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7168</v>
+        <v>1.3718</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6546</v>
+        <v>1.2635</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3273</v>
+        <v>-1.8381</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1716</v>
+        <v>-0.6146</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1557</v>
+        <v>-1.2235</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5531</v>
+        <v>-0.5431</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0902</v>
+        <v>-0.0384</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5371</v>
+        <v>-0.5047</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1283</v>
+        <v>0.894</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1283</v>
+        <v>0.894</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0801</v>
+        <v>0.1529</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6882</v>
+        <v>-0.7277</v>
       </c>
       <c r="F5" t="n">
-        <v>0.608</v>
+        <v>0.8806</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4929</v>
@@ -844,13 +844,13 @@
         <v>0.3881</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0247</v>
+        <v>0.2577</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2434</v>
+        <v>0.2038</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2187</v>
+        <v>0.0538</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1656</v>
+        <v>0.0619</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3081</v>
+        <v>0.5083</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4737</v>
+        <v>-0.4464</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7989000000000001</v>
@@ -922,13 +922,13 @@
         <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2488</v>
+        <v>-0.0213</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.424</v>
+        <v>-0.2238</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1752</v>
+        <v>0.2025</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2947</v>
+        <v>-1.2674</v>
       </c>
       <c r="E7" t="n">
         <v>-0.8284</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4663</v>
+        <v>-0.439</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3252</v>
@@ -1000,13 +1000,13 @@
         <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1635</v>
+        <v>-0.1363</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7032</v>
+        <v>-1.5256</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4393</v>
+        <v>-0.1993</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2639</v>
+        <v>-1.3263</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7283</v>
+        <v>-0.4274</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4096</v>
+        <v>0.1343</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3187</v>
+        <v>-0.5617</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4871</v>
+        <v>1.5493</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2842</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7713</v>
+        <v>0.8119</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2154</v>
+        <v>-1.9767</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1254</v>
+        <v>-0.6031</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.09</v>
+        <v>-1.3737</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2371</v>
+        <v>0.1063</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4497</v>
+        <v>-0.062</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2126</v>
+        <v>0.1683</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5642</v>
+        <v>-0.2343</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5642</v>
+        <v>1.2239</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.4582</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0135</v>
+        <v>-1.8127</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4727</v>
+        <v>-0.7396</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4862</v>
+        <v>-1.0731</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1126</v>
+        <v>-1.7283</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7771</v>
+        <v>-1.4096</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6645</v>
+        <v>-0.3187</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8888</v>
+        <v>0.4871</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2678</v>
+        <v>-0.2842</v>
       </c>
       <c r="L9" t="n">
-        <v>2.621</v>
+        <v>0.7713</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.0014</v>
+        <v>-2.2154</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0449</v>
+        <v>-1.1254</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9565</v>
+        <v>-1.09</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9702</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9403</v>
+        <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5648</v>
+        <v>0.1276</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5421</v>
+        <v>0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0227</v>
+        <v>-0.0219</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4955</v>
+        <v>0.5642</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0478</v>
+        <v>0.5642</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1865</v>
+        <v>-2.062</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5947</v>
+        <v>-2.3339</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4082</v>
+        <v>0.2719</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0288</v>
@@ -1234,13 +1234,13 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1278</v>
+        <v>-0.0034</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3634</v>
+        <v>-0.1026</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2355</v>
+        <v>0.0993</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2239</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3436</v>
+        <v>-2.2285</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.011</v>
+        <v>-2.9504</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6675</v>
+        <v>0.722</v>
       </c>
       <c r="G11" t="n">
         <v>0.276</v>
@@ -1312,13 +1312,13 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2912</v>
+        <v>-0.1761</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1211</v>
+        <v>-0.0606</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.17</v>
+        <v>-0.1155</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5049</v>
+        <v>-3.0629</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9605</v>
+        <v>0.5322</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5444</v>
+        <v>-3.5952</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4274</v>
+        <v>-0.1126</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1343</v>
+        <v>-1.7771</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5617</v>
+        <v>1.6645</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5493</v>
+        <v>2.8888</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.2678</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8119</v>
+        <v>2.621</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9767</v>
+        <v>-3.0014</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6031</v>
+        <v>-2.0449</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3737</v>
+        <v>-0.9565</v>
       </c>
       <c r="P12" t="n">
         <v>-0.9702</v>
@@ -1390,22 +1390,22 @@
         <v>1.9403</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.873</v>
+        <v>0.5154</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8233</v>
+        <v>0.6017</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0498</v>
+        <v>-0.0863</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2343</v>
+        <v>-2.4955</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2239</v>
+        <v>-0.0478</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4582</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1328</v>
+        <v>-5.9765</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7463</v>
+        <v>-5.7263</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3865</v>
+        <v>-0.2502</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2745</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0805</v>
+        <v>1.2368</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7608</v>
+        <v>0.7809</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3197</v>
+        <v>0.456</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2821</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.3522</v>
+        <v>-13.4435</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.738</v>
+        <v>-10.8295</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.614199999999999</v>
+        <v>-2.614</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.872199999999999</v>
+        <v>-4.8722</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.513700000000001</v>
+        <v>-7.5137</v>
       </c>
       <c r="I14" t="n">
         <v>2.6416</v>
       </c>
       <c r="J14" t="n">
-        <v>8.722099999999999</v>
+        <v>8.722100000000001</v>
       </c>
       <c r="K14" t="n">
         <v>-0.1480000000000002</v>
@@ -1531,10 +1531,10 @@
         <v>-13.5943</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.365600000000001</v>
+        <v>-7.3656</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.2286</v>
+        <v>-6.228600000000001</v>
       </c>
       <c r="P14" t="n">
         <v>-9.701699999999999</v>
@@ -1546,16 +1546,16 @@
         <v>15.5226</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2114</v>
+        <v>2.1199</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4369999999999998</v>
+        <v>1.3456</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7742999999999998</v>
+        <v>0.7743</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9895999999999998</v>
+        <v>-0.9895999999999996</v>
       </c>
       <c r="W14" t="n">
         <v>4.3268</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1849</v>
+        <v>5.464</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6493</v>
+        <v>3.8495</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5356</v>
+        <v>1.6145</v>
       </c>
       <c r="G15" t="n">
         <v>2.5866</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4614</v>
+        <v>-0.1822</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3634</v>
+        <v>-0.1632</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.098</v>
+        <v>-0.0191</v>
       </c>
       <c r="V15" t="n">
         <v>3.0597</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8188</v>
+        <v>4.6163</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1656</v>
+        <v>1.6661</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6532</v>
+        <v>2.9502</v>
       </c>
       <c r="G16" t="n">
         <v>1.1277</v>
@@ -1702,13 +1702,13 @@
         <v>3.1045</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4432</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0779</v>
+        <v>-0.5774</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3654</v>
+        <v>-0.0684</v>
       </c>
       <c r="V16" t="n">
         <v>1.2239</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7387</v>
+        <v>3.6809</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9801</v>
+        <v>0.6798</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7586</v>
+        <v>3.0011</v>
       </c>
       <c r="G17" t="n">
         <v>2.6864</v>
@@ -1780,13 +1780,13 @@
         <v>2.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5583</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4262</v>
+        <v>0.1259</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1321</v>
+        <v>0.3746</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2821</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7141</v>
+        <v>3.0572</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0068</v>
+        <v>1.4072</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7073</v>
+        <v>1.65</v>
       </c>
       <c r="G18" t="n">
         <v>1.4093</v>
@@ -1858,13 +1858,13 @@
         <v>2.1344</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2371</v>
+        <v>0.106</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4845</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2474</v>
+        <v>0.1901</v>
       </c>
       <c r="V18" t="n">
         <v>0.3776</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>D. SHIELDS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9613</v>
+        <v>1.1915</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0969</v>
+        <v>0.2683</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0582</v>
+        <v>0.9233</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9814000000000001</v>
+        <v>1.5308</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4531</v>
+        <v>1.7054</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5283</v>
+        <v>-0.1746</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5057</v>
+        <v>1.571</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1895</v>
+        <v>1.6066</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6952</v>
+        <v>-0.0356</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4871</v>
+        <v>-0.0402</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2637</v>
+        <v>0.0989</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2235</v>
+        <v>-0.139</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9105</v>
+        <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5334</v>
+        <v>-0.5333</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1683</v>
+        <v>-0.3326</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3652</v>
+        <v>-0.2007</v>
       </c>
       <c r="V19" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9186</v>
+        <v>1.1492</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2693</v>
+        <v>-0.0969</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3507</v>
+        <v>1.2462</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6703</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9895</v>
+        <v>-0.4531</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3192</v>
+        <v>-0.5283</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2507</v>
+        <v>0.5057</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6189</v>
+        <v>-0.1895</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6318</v>
+        <v>0.6952</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5804</v>
+        <v>-1.4871</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6294</v>
+        <v>-0.2637</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.951</v>
+        <v>-1.2235</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9702</v>
+        <v>2.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3946</v>
+        <v>-0.3454</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1828</v>
+        <v>-0.1683</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2118</v>
+        <v>-0.1772</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0478</v>
+        <v>1.506</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. SHIELDS</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8278</v>
+        <v>1.0175</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.5847</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597</v>
+        <v>1.6022</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5308</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7054</v>
+        <v>1.1023</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1746</v>
+        <v>-2.0131</v>
       </c>
       <c r="J21" t="n">
-        <v>1.571</v>
+        <v>-0.6096</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6066</v>
+        <v>0.725</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0356</v>
+        <v>-1.3347</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0402</v>
+        <v>-0.3011</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0989</v>
+        <v>0.3773</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.139</v>
+        <v>-0.6785</v>
       </c>
       <c r="P21" t="n">
-        <v>0.194</v>
+        <v>1.7463</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1642</v>
+        <v>1.9403</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.897</v>
+        <v>-0.1001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.0631</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3643</v>
+        <v>-0.037</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.9247</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.885</v>
+        <v>1.1692</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6022</v>
+        <v>-0.2445</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9108000000000001</v>
+        <v>0.6703</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1023</v>
+        <v>0.9895</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0131</v>
+        <v>-0.3192</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6096</v>
+        <v>2.2507</v>
       </c>
       <c r="K22" t="n">
-        <v>0.725</v>
+        <v>1.6189</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3347</v>
+        <v>0.6318</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3011</v>
+        <v>-1.5804</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3773</v>
+        <v>-0.6294</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6785</v>
+        <v>-0.951</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7463</v>
+        <v>-0.194</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4004</v>
+        <v>0.4007</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3634</v>
+        <v>0.0827</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.037</v>
+        <v>0.318</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2821</v>
+        <v>0.0478</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0313</v>
+        <v>0.1689</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0799</v>
+        <v>0.1203</v>
       </c>
       <c r="F23" t="n">
         <v>0.0486</v>
@@ -2248,10 +2248,10 @@
         <v>0.194</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.194</v>
+        <v>0.0062</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1211</v>
+        <v>0.0791</v>
       </c>
       <c r="U23" t="n">
         <v>-0.07290000000000001</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>M. RUBIO CORCHADO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5666</v>
+        <v>-1.6443</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9772</v>
+        <v>-1.0243</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4107</v>
+        <v>-0.6199</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0211</v>
+        <v>-2.0582</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.2417</v>
+        <v>-1.0727</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2206</v>
+        <v>-0.9855</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6712</v>
+        <v>-0.226</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.8331</v>
+        <v>-0.4696</v>
       </c>
       <c r="L24" t="n">
-        <v>2.5043</v>
+        <v>0.2436</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6923</v>
+        <v>-1.8321</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4087</v>
+        <v>-0.6031</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2836</v>
+        <v>-1.229</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R24" t="n">
-        <v>2.9105</v>
+        <v>2.5224</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5038</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8636</v>
+        <v>-0.1102</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6402</v>
+        <v>0.1957</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8254</v>
+        <v>-1.2239</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3776</v>
+        <v>0.2821</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4477</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.6381</v>
+        <v>-1.67</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1614</v>
+        <v>-1.778</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5233</v>
+        <v>0.1081</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.136</v>
+        <v>-0.0211</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-2.2417</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0611</v>
+        <v>2.2206</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1336</v>
+        <v>0.6712</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0288</v>
+        <v>-1.8331</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1624</v>
+        <v>2.5043</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.2696</v>
+        <v>-0.6923</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0462</v>
+        <v>-0.4087</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2235</v>
+        <v>-0.2836</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9105</v>
+        <v>-2.1344</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5224</v>
+        <v>2.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>1.0621</v>
+        <v>0.4004</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2752</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2131</v>
+        <v>0.3376</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.1761</v>
+        <v>-2.8254</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.6597</v>
+        <v>-0.3776</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5164</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. RUBIO CORCHADO</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.2933</v>
+        <v>-2.2692</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.3246</v>
+        <v>-3.0623</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9686</v>
+        <v>0.7931</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.0582</v>
+        <v>-1.136</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.0727</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9855</v>
+        <v>-1.0611</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.226</v>
+        <v>0.1336</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4696</v>
+        <v>-0.0288</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2436</v>
+        <v>0.1624</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.8321</v>
+        <v>-1.2696</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.6031</v>
+        <v>-0.0462</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.229</v>
+        <v>-1.2235</v>
       </c>
       <c r="P26" t="n">
-        <v>1.5523</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R26" t="n">
         <v>2.5224</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5635</v>
+        <v>0.431</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4105</v>
+        <v>0.3743</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.153</v>
+        <v>0.0567</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2239</v>
+        <v>-1.1761</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2821</v>
+        <v>-0.6597</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.506</v>
+        <v>-0.5164</v>
       </c>
     </row>
     <row r="27">
@@ -2515,22 +2515,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>14.35209999999999</v>
+        <v>15.6867</v>
       </c>
       <c r="E27" t="n">
-        <v>2.6142</v>
+        <v>2.614199999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>11.7381</v>
+        <v>13.0729</v>
       </c>
       <c r="G27" t="n">
-        <v>4.872299999999999</v>
+        <v>4.872300000000001</v>
       </c>
       <c r="H27" t="n">
         <v>7.513700000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.641399999999999</v>
+        <v>-2.6414</v>
       </c>
       <c r="J27" t="n">
         <v>13.5945</v>
@@ -2539,19 +2539,19 @@
         <v>7.365599999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>6.228800000000001</v>
+        <v>6.2288</v>
       </c>
       <c r="M27" t="n">
         <v>-8.7219</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1481000000000001</v>
+        <v>0.1481000000000002</v>
       </c>
       <c r="O27" t="n">
         <v>-8.870200000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>9.701600000000001</v>
+        <v>9.701599999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>-15.5227</v>
@@ -2560,16 +2560,16 @@
         <v>25.2242</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.2112</v>
+        <v>0.1235999999999998</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.7741000000000008</v>
+        <v>-0.7741</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4374</v>
+        <v>0.8974</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9895999999999998</v>
+        <v>0.9895999999999994</v>
       </c>
       <c r="W27" t="n">
         <v>5.3165</v>
